--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.43.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.43.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.43.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.43.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="48" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -594,7 +594,7 @@
       <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | localized OCR phrase divergence vs other OCR: "" vs "XXXI" :: XXXI. 31 of 1845, which is in the following words :â€”</t>
+          <t>L86: localized OCR phrase divergence vs other OCR: "" vs "XXXI" :: XXXI. 31 of 1845, which is in the following words :—</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
@@ -605,16 +605,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: of a Subp Ã¦ na to app</t>
+          <t>L22: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€ž1 i Order The above Order 24 is taken from the English Order</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]36 ABSENT DEFENDANTS.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]36 ABSENT DEFENDANTS.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L10: isolated marker/symbol line :: 36</t>
@@ -657,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -672,14 +676,10 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: sh Order, the words are â€œSubpana to appear to</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | localized OCR phrase divergence vs other OCR: "" vs "XXXI" :: XXXI. 31 of 1845, which is in the following words :â€”</t>
-        </is>
-      </c>
+          <t>L36: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -727,7 +727,7 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: SubpÃ¦na to appear merely.</t>
+          <t>L57: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr"/>
@@ -735,7 +735,7 @@
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L22: isolated marker/symbol line :: â†’</t>
+          <t>L22: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr"/>
@@ -758,7 +758,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -774,7 +774,7 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr"/>
@@ -819,17 +819,13 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: 2</t>
+          <t>L36: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -872,7 +868,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L52: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -915,7 +911,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L57: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -958,7 +954,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: 1</t>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -981,12 +977,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1001,7 +997,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: 7</t>
+          <t>L73: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1029,7 +1025,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1044,7 +1040,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L75: isolated marker/symbol line :: 9</t>
+          <t>L74: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1067,7 +1063,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1087,7 +1083,7 @@
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 2</t>
+          <t>L75: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr"/>
@@ -1128,7 +1124,11 @@
       <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
-      <c r="N13" s="1" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>L76: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
       <c r="O13" s="1" t="inlineStr"/>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
